--- a/artfynd/A 54192-2025 artfynd.xlsx
+++ b/artfynd/A 54192-2025 artfynd.xlsx
@@ -907,45 +907,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133347531</v>
+        <v>133346532</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577222</v>
+        <v>577240</v>
       </c>
       <c r="R4" t="n">
-        <v>7054011</v>
+        <v>7054044</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,49 +1018,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133346532</v>
+        <v>133347531</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577240</v>
+        <v>577222</v>
       </c>
       <c r="R5" t="n">
-        <v>7054044</v>
+        <v>7054011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133347071</v>
+        <v>133346584</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1461,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577257</v>
+        <v>577241</v>
       </c>
       <c r="R9" t="n">
-        <v>7054002</v>
+        <v>7054044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133346584</v>
+        <v>133347071</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577241</v>
+        <v>577257</v>
       </c>
       <c r="R10" t="n">
-        <v>7054044</v>
+        <v>7054002</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2322,45 +2322,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133347635</v>
+        <v>133347991</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577232</v>
+        <v>577254</v>
       </c>
       <c r="R17" t="n">
-        <v>7054000</v>
+        <v>7054085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,49 +2433,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133347991</v>
+        <v>133347635</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577254</v>
+        <v>577232</v>
       </c>
       <c r="R18" t="n">
-        <v>7054085</v>
+        <v>7054000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 54192-2025 artfynd.xlsx
+++ b/artfynd/A 54192-2025 artfynd.xlsx
@@ -786,59 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133348764</v>
+        <v>133347531</v>
       </c>
       <c r="B3" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577340</v>
+        <v>577222</v>
       </c>
       <c r="R3" t="n">
-        <v>7054130</v>
+        <v>7054011</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +893,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133346532</v>
+        <v>133348764</v>
       </c>
       <c r="B4" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577240</v>
+        <v>577340</v>
       </c>
       <c r="R4" t="n">
-        <v>7054044</v>
+        <v>7054130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,45 +1014,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133347531</v>
+        <v>133346532</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577222</v>
+        <v>577240</v>
       </c>
       <c r="R5" t="n">
-        <v>7054011</v>
+        <v>7054044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1450,45 +1450,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133346584</v>
+        <v>133347315</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577241</v>
+        <v>577227</v>
       </c>
       <c r="R9" t="n">
-        <v>7054044</v>
+        <v>7054013</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1534,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133347071</v>
+        <v>133346584</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,21 +1572,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577257</v>
+        <v>577241</v>
       </c>
       <c r="R10" t="n">
-        <v>7054002</v>
+        <v>7054044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1631,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1637,7 +1641,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,49 +1668,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133347315</v>
+        <v>133347071</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577227</v>
+        <v>577257</v>
       </c>
       <c r="R11" t="n">
-        <v>7054013</v>
+        <v>7054002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,45 +1775,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133347432</v>
+        <v>133348157</v>
       </c>
       <c r="B12" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577231</v>
+        <v>577269</v>
       </c>
       <c r="R12" t="n">
-        <v>7054016</v>
+        <v>7054084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1855,7 +1859,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,49 +1886,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133348157</v>
+        <v>133347432</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577269</v>
+        <v>577231</v>
       </c>
       <c r="R13" t="n">
-        <v>7054084</v>
+        <v>7054016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2322,49 +2322,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133347991</v>
+        <v>133347635</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577254</v>
+        <v>577232</v>
       </c>
       <c r="R17" t="n">
-        <v>7054085</v>
+        <v>7054000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2433,45 +2429,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133347635</v>
+        <v>133347991</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577232</v>
+        <v>577254</v>
       </c>
       <c r="R18" t="n">
-        <v>7054000</v>
+        <v>7054085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 54192-2025 artfynd.xlsx
+++ b/artfynd/A 54192-2025 artfynd.xlsx
@@ -786,45 +786,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133347531</v>
+        <v>133346532</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577222</v>
+        <v>577240</v>
       </c>
       <c r="R3" t="n">
-        <v>7054011</v>
+        <v>7054044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,59 +897,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133348764</v>
+        <v>133347531</v>
       </c>
       <c r="B4" t="n">
-        <v>57145</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577340</v>
+        <v>577222</v>
       </c>
       <c r="R4" t="n">
-        <v>7054130</v>
+        <v>7054011</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +1004,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133346532</v>
+        <v>133348764</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>57145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577240</v>
+        <v>577340</v>
       </c>
       <c r="R5" t="n">
-        <v>7054044</v>
+        <v>7054130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1450,49 +1450,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133347315</v>
+        <v>133346584</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577227</v>
+        <v>577241</v>
       </c>
       <c r="R9" t="n">
-        <v>7054013</v>
+        <v>7054044</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1520,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133346584</v>
+        <v>133347071</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577241</v>
+        <v>577257</v>
       </c>
       <c r="R10" t="n">
-        <v>7054044</v>
+        <v>7054002</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1627,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1637,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,45 +1664,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133347071</v>
+        <v>133347315</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577257</v>
+        <v>577227</v>
       </c>
       <c r="R11" t="n">
-        <v>7054002</v>
+        <v>7054013</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,49 +1775,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133348157</v>
+        <v>133347432</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577269</v>
+        <v>577231</v>
       </c>
       <c r="R12" t="n">
-        <v>7054084</v>
+        <v>7054016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1845,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1859,7 +1855,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,45 +1882,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133347432</v>
+        <v>133348157</v>
       </c>
       <c r="B13" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577231</v>
+        <v>577269</v>
       </c>
       <c r="R13" t="n">
-        <v>7054016</v>
+        <v>7054084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2322,45 +2322,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133347635</v>
+        <v>133347991</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577232</v>
+        <v>577254</v>
       </c>
       <c r="R17" t="n">
-        <v>7054000</v>
+        <v>7054085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,49 +2433,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133347991</v>
+        <v>133347635</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577254</v>
+        <v>577232</v>
       </c>
       <c r="R18" t="n">
-        <v>7054085</v>
+        <v>7054000</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 54192-2025 artfynd.xlsx
+++ b/artfynd/A 54192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133326933</v>
+        <v>133347167</v>
       </c>
       <c r="B2" t="n">
-        <v>99178</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577257</v>
+        <v>577264</v>
       </c>
       <c r="R2" t="n">
-        <v>7054040</v>
+        <v>7053990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133347531</v>
+        <v>133346691</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577222</v>
+        <v>577243</v>
       </c>
       <c r="R3" t="n">
-        <v>7054011</v>
+        <v>7054046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133346532</v>
+        <v>133346783</v>
       </c>
       <c r="B4" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,38 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577240</v>
+        <v>577237</v>
       </c>
       <c r="R4" t="n">
-        <v>7054044</v>
+        <v>7054030</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,59 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133348764</v>
+        <v>133347071</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577340</v>
+        <v>577257</v>
       </c>
       <c r="R5" t="n">
-        <v>7054130</v>
+        <v>7054002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133348528</v>
+        <v>133347531</v>
       </c>
       <c r="B6" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,38 +1114,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577341</v>
+        <v>577222</v>
       </c>
       <c r="R6" t="n">
-        <v>7054066</v>
+        <v>7054011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1209,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,14 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133348609</v>
+        <v>133347635</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1271,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577340</v>
+        <v>577232</v>
       </c>
       <c r="R7" t="n">
-        <v>7054061</v>
+        <v>7054000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,14 +1317,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133346691</v>
+        <v>133348609</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1378,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577243</v>
+        <v>577340</v>
       </c>
       <c r="R8" t="n">
-        <v>7054046</v>
+        <v>7054061</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1423,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133346584</v>
+        <v>133347432</v>
       </c>
       <c r="B9" t="n">
-        <v>80473</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577241</v>
+        <v>577231</v>
       </c>
       <c r="R9" t="n">
-        <v>7054044</v>
+        <v>7054016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1530,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,49 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133347315</v>
+        <v>133346584</v>
       </c>
       <c r="B10" t="n">
-        <v>99178</v>
+        <v>80488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577227</v>
+        <v>577241</v>
       </c>
       <c r="R10" t="n">
-        <v>7054013</v>
+        <v>7054044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,45 +1638,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133347071</v>
+        <v>133348764</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577257</v>
+        <v>577340</v>
       </c>
       <c r="R11" t="n">
-        <v>7054002</v>
+        <v>7054130</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133348157</v>
+        <v>133326933</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577269</v>
+        <v>577257</v>
       </c>
       <c r="R12" t="n">
-        <v>7054084</v>
+        <v>7054040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,22 +1828,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1886,45 +1870,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133347432</v>
+        <v>133346172</v>
       </c>
       <c r="B13" t="n">
-        <v>79115</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577231</v>
+        <v>577209</v>
       </c>
       <c r="R13" t="n">
-        <v>7054016</v>
+        <v>7054060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1944,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1966,7 +1954,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133349356</v>
+        <v>133346532</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,7 +2011,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2032,10 +2020,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577246</v>
+        <v>577240</v>
       </c>
       <c r="R14" t="n">
-        <v>7054120</v>
+        <v>7054044</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2067,7 +2055,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2065,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,45 +2092,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133346783</v>
+        <v>133347315</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577237</v>
+        <v>577227</v>
       </c>
       <c r="R15" t="n">
-        <v>7054030</v>
+        <v>7054013</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2184,7 +2176,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2211,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133348650</v>
+        <v>133347991</v>
       </c>
       <c r="B16" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,7 +2233,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2250,10 +2242,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577352</v>
+        <v>577254</v>
       </c>
       <c r="R16" t="n">
-        <v>7054068</v>
+        <v>7054085</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2277,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2295,7 +2287,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,45 +2314,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133347635</v>
+        <v>133348157</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577232</v>
+        <v>577269</v>
       </c>
       <c r="R17" t="n">
-        <v>7054000</v>
+        <v>7054084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,7 +2388,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2402,7 +2398,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2429,10 +2425,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133347991</v>
+        <v>133348528</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,7 +2455,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2468,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577254</v>
+        <v>577341</v>
       </c>
       <c r="R18" t="n">
-        <v>7054085</v>
+        <v>7054066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,7 +2499,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2513,7 +2509,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2537,6 +2533,228 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133348650</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577352</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7054068</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133349356</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577246</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7054120</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54192-2025 artfynd.xlsx
+++ b/artfynd/A 54192-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347167</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133346691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133346783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347071</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133348609</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347432</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133346584</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133348764</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133326933</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133346172</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133346532</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2200,6 +2270,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347315</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2311,6 +2386,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133347991</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133348157</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2533,6 +2618,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133348528</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133348650</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2755,8 +2850,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133349356</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>